--- a/kidscorner/Filter Page/KidsCorner_Filter_Page.xlsx
+++ b/kidscorner/Filter Page/KidsCorner_Filter_Page.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piabo\Documents\P Studio\Projects\Ongoing Projects\Spia\KidsCorner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piabo\Documents\GitHub\spia-s.github.io\kidscorner\Filter Page\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C145A91-282E-47CD-BD5D-6E46458BB046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1C6B17-330C-4B13-B73F-2848AD74BC99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="1965" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18780" yWindow="3030" windowWidth="10185" windowHeight="10575" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="🎛️ Filter UI Structure" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="372">
   <si>
     <t>KidsCorner — Filter Page Structure</t>
   </si>
@@ -1132,6 +1132,12 @@
   </si>
   <si>
     <t>Classic=dark green, Bestseller=orange, Award-winner=gold, Modern Classic=teal, Cultural Classic=brown</t>
+  </si>
+  <si>
+    <t>Illustrated</t>
+  </si>
+  <si>
+    <t>Text-heavy</t>
   </si>
 </sst>
 </file>
@@ -1690,66 +1696,78 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1767,18 +1785,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2095,7 +2101,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="73"/>
@@ -2107,7 +2113,7 @@
       <c r="H1" s="73"/>
     </row>
     <row r="2" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="90" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="73"/>
@@ -2120,7 +2126,7 @@
     </row>
     <row r="3" spans="1:8" ht="10" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="89" t="s">
+      <c r="A4" s="72" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="73"/>
@@ -2133,15 +2139,15 @@
     </row>
     <row r="5" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="6" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="84" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="73"/>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="91" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="73"/>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="85" t="s">
         <v>5</v>
       </c>
       <c r="F6" s="73"/>
@@ -2151,11 +2157,11 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="87" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="73"/>
-      <c r="C7" s="90" t="s">
+      <c r="C7" s="75" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="73"/>
@@ -2173,11 +2179,11 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="81"/>
+      <c r="A8" s="74"/>
       <c r="B8" s="73"/>
-      <c r="C8" s="76"/>
+      <c r="C8" s="78"/>
       <c r="D8" s="73"/>
-      <c r="E8" s="91" t="s">
+      <c r="E8" s="76" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="73"/>
@@ -2186,11 +2192,11 @@
     </row>
     <row r="9" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="10" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="77" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="73"/>
-      <c r="C10" s="82" t="s">
+      <c r="C10" s="86" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="73"/>
@@ -2208,11 +2214,11 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="77" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="73"/>
-      <c r="C11" s="86" t="s">
+      <c r="C11" s="89" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="73"/>
@@ -2230,11 +2236,11 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="77" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="73"/>
-      <c r="C12" s="85" t="s">
+      <c r="C12" s="88" t="s">
         <v>27</v>
       </c>
       <c r="D12" s="73"/>
@@ -2252,11 +2258,11 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="77" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="73"/>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="79" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="73"/>
@@ -2274,11 +2280,11 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="74" t="s">
+      <c r="A14" s="77" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="73"/>
-      <c r="C14" s="77" t="s">
+      <c r="C14" s="92" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="73"/>
@@ -2296,14 +2302,14 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="74" t="s">
+      <c r="A15" s="77" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="73"/>
-      <c r="C15" s="76"/>
+      <c r="C15" s="78"/>
       <c r="D15" s="73"/>
       <c r="E15" s="8" t="s">
-        <v>10</v>
+        <v>370</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>45</v>
@@ -2316,11 +2322,13 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="81"/>
+      <c r="A16" s="74"/>
       <c r="B16" s="73"/>
-      <c r="C16" s="76"/>
+      <c r="C16" s="78"/>
       <c r="D16" s="73"/>
-      <c r="E16" s="12"/>
+      <c r="E16" s="8" t="s">
+        <v>371</v>
+      </c>
       <c r="F16" s="13"/>
       <c r="G16" s="14"/>
       <c r="H16" s="11" t="s">
@@ -2328,9 +2336,9 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="81"/>
+      <c r="A17" s="74"/>
       <c r="B17" s="73"/>
-      <c r="C17" s="76"/>
+      <c r="C17" s="78"/>
       <c r="D17" s="73"/>
       <c r="E17" s="12"/>
       <c r="F17" s="13"/>
@@ -2340,9 +2348,9 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="81"/>
+      <c r="A18" s="74"/>
       <c r="B18" s="73"/>
-      <c r="C18" s="76"/>
+      <c r="C18" s="78"/>
       <c r="D18" s="73"/>
       <c r="E18" s="12"/>
       <c r="F18" s="13"/>
@@ -2352,9 +2360,9 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="81"/>
+      <c r="A19" s="74"/>
       <c r="B19" s="73"/>
-      <c r="C19" s="76"/>
+      <c r="C19" s="78"/>
       <c r="D19" s="73"/>
       <c r="E19" s="12"/>
       <c r="F19" s="13"/>
@@ -2364,9 +2372,9 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="81"/>
+      <c r="A20" s="74"/>
       <c r="B20" s="73"/>
-      <c r="C20" s="76"/>
+      <c r="C20" s="78"/>
       <c r="D20" s="73"/>
       <c r="E20" s="12"/>
       <c r="F20" s="13"/>
@@ -2376,9 +2384,9 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="81"/>
+      <c r="A21" s="74"/>
       <c r="B21" s="73"/>
-      <c r="C21" s="76"/>
+      <c r="C21" s="78"/>
       <c r="D21" s="73"/>
       <c r="E21" s="12"/>
       <c r="F21" s="13"/>
@@ -2388,9 +2396,9 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="81"/>
+      <c r="A22" s="74"/>
       <c r="B22" s="73"/>
-      <c r="C22" s="76"/>
+      <c r="C22" s="78"/>
       <c r="D22" s="73"/>
       <c r="E22" s="12"/>
       <c r="F22" s="13"/>
@@ -2401,7 +2409,7 @@
     </row>
     <row r="24" spans="1:8" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="25" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="E25" s="84" t="s">
+      <c r="E25" s="82" t="s">
         <v>55</v>
       </c>
       <c r="F25" s="73"/>
@@ -2470,7 +2478,7 @@
       <c r="H30" s="15"/>
     </row>
     <row r="32" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="88" t="s">
+      <c r="A32" s="81" t="s">
         <v>65</v>
       </c>
       <c r="B32" s="73"/>
@@ -2485,7 +2493,7 @@
       <c r="A33" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="80" t="s">
         <v>67</v>
       </c>
       <c r="C33" s="73"/>
@@ -2499,7 +2507,7 @@
       <c r="A34" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="75" t="s">
+      <c r="B34" s="80" t="s">
         <v>69</v>
       </c>
       <c r="C34" s="73"/>
@@ -2513,7 +2521,7 @@
       <c r="A35" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="75" t="s">
+      <c r="B35" s="80" t="s">
         <v>71</v>
       </c>
       <c r="C35" s="73"/>
@@ -2527,7 +2535,7 @@
       <c r="A36" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="75" t="s">
+      <c r="B36" s="80" t="s">
         <v>73</v>
       </c>
       <c r="C36" s="73"/>
@@ -2541,7 +2549,7 @@
       <c r="A37" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B37" s="75" t="s">
+      <c r="B37" s="80" t="s">
         <v>75</v>
       </c>
       <c r="C37" s="73"/>
@@ -2555,7 +2563,7 @@
       <c r="A38" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B38" s="75" t="s">
+      <c r="B38" s="80" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="73"/>
@@ -2569,7 +2577,7 @@
       <c r="A39" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B39" s="75" t="s">
+      <c r="B39" s="80" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="73"/>
@@ -2583,7 +2591,7 @@
       <c r="A40" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B40" s="75" t="s">
+      <c r="B40" s="80" t="s">
         <v>81</v>
       </c>
       <c r="C40" s="73"/>
@@ -2597,7 +2605,7 @@
       <c r="A41" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B41" s="75" t="s">
+      <c r="B41" s="80" t="s">
         <v>83</v>
       </c>
       <c r="C41" s="73"/>
@@ -2611,7 +2619,7 @@
       <c r="A42" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B42" s="75" t="s">
+      <c r="B42" s="80" t="s">
         <v>85</v>
       </c>
       <c r="C42" s="73"/>
@@ -2623,16 +2631,27 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A8:B8"/>
@@ -2649,29 +2668,18 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="B39:H39"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="B33:H33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2690,7 +2698,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="93" t="s">
         <v>86</v>
       </c>
       <c r="B1" s="73"/>
@@ -2703,7 +2711,7 @@
       <c r="I1" s="73"/>
     </row>
     <row r="2" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="98" t="s">
         <v>87</v>
       </c>
       <c r="B2" s="73"/>
@@ -2745,7 +2753,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="102" t="s">
+      <c r="A4" s="96" t="s">
         <v>92</v>
       </c>
       <c r="B4" s="73"/>
@@ -2932,7 +2940,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="95" t="s">
+      <c r="A11" s="99" t="s">
         <v>105</v>
       </c>
       <c r="B11" s="73"/>
@@ -3090,7 +3098,7 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="94" t="s">
         <v>137</v>
       </c>
       <c r="B17" s="73"/>
@@ -3103,7 +3111,7 @@
       <c r="I17" s="73"/>
     </row>
     <row r="18" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="101" t="s">
+      <c r="A18" s="95" t="s">
         <v>138</v>
       </c>
       <c r="B18" s="73"/>
@@ -3290,7 +3298,7 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="93" t="s">
+      <c r="A25" s="97" t="s">
         <v>170</v>
       </c>
       <c r="B25" s="73"/>
@@ -3477,7 +3485,7 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="98" t="s">
+      <c r="A32" s="102" t="s">
         <v>197</v>
       </c>
       <c r="B32" s="73"/>
@@ -3751,7 +3759,7 @@
       </c>
     </row>
     <row r="42" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="97" t="s">
+      <c r="A42" s="101" t="s">
         <v>236</v>
       </c>
       <c r="B42" s="73"/>
@@ -3938,7 +3946,7 @@
       </c>
     </row>
     <row r="49" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="96" t="s">
+      <c r="A49" s="100" t="s">
         <v>259</v>
       </c>
       <c r="B49" s="73"/>
@@ -4329,6 +4337,9 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
@@ -4336,9 +4347,6 @@
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A32:I32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4356,7 +4364,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="93" t="s">
         <v>320</v>
       </c>
       <c r="B1" s="73"/>
@@ -4364,7 +4372,7 @@
       <c r="D1" s="73"/>
     </row>
     <row r="2" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="90" t="s">
         <v>321</v>
       </c>
       <c r="B2" s="73"/>
